--- a/datasets/agenda_implementation/data/output/agenda_items.xlsx
+++ b/datasets/agenda_implementation/data/output/agenda_items.xlsx
@@ -2351,15 +2351,15 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Fitness check on the legislative acquis in the digital policy area</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Fitness check on the legislative acquis in the digital policy area</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2381,15 +2381,15 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Fitness check on energy security architecture</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Fitness check on energy security architecture</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2411,15 +2411,15 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
+          <t>Fitness check on market access in inland waterway transport</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>Q2 / Q3 2025</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Fitness check on market access in inland waterway transport</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2441,15 +2441,15 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Fitness Check of EU airports legislation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Fitness Check of EU airports legislation</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2471,15 +2471,15 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Evaluation of the Public Procurement Directives</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Evaluation of the Public Procurement Directives</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2501,15 +2501,15 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
+          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2531,15 +2531,15 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2561,15 +2561,15 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Evaluation of radioactive waste directives</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Evaluation of radioactive waste directives</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2591,15 +2591,15 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
+          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2621,15 +2621,15 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
+          <t>Evaluation of the EU Lifts Directive</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Evaluation of the EU Lifts Directive</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2651,15 +2651,15 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
+          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2681,15 +2681,15 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2711,15 +2711,15 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Evaluation of the Fishing Vessel Safety Directive</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>Q1/Q2 2025</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Evaluation of the Fishing Vessel Safety Directive</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2741,15 +2741,15 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
+          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2771,15 +2771,15 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
+          <t>Evaluation of State aid rules for banks in difficulties</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Evaluation of State aid rules for banks in difficulties</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2801,15 +2801,15 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
+          <t>Evaluation of the Guarantee Notice</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Evaluation of the Guarantee Notice</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -2831,15 +2831,15 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
+          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -2861,15 +2861,15 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
+          <t>Evaluation of EU Rules of Origin</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Evaluation of EU Rules of Origin</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2891,15 +2891,15 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
+          <t>Evaluation of the Defence Transfers Directive</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Evaluation of the Defence Transfers Directive</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2921,15 +2921,15 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Evaluation of the Firearms Directive</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Evaluation of the Firearms Directive</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -2951,15 +2951,15 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
+          <t>Evaluation on the Innovation Fund</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Evaluation on the Innovation Fund</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -2981,15 +2981,15 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
+          <t>Evaluation on the Modernisation Fund</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Evaluation on the Modernisation Fund</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3011,15 +3011,15 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
+          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3041,15 +3041,15 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>Q3/Q4 2025</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -3071,15 +3071,15 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -3101,15 +3101,15 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -3131,15 +3131,15 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3161,15 +3161,15 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -3191,15 +3191,15 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
+          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -3221,15 +3221,15 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
+          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -3251,15 +3251,15 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
+          <t>Interim Evaluation of the European Defence Fund</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>Q1-Q2 2025</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Interim Evaluation of the European Defence Fund</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -3281,15 +3281,15 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
+          <t>Interim evaluation of the Customs 2021-2027 programme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Interim evaluation of the Customs 2021-2027 programme</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -3311,15 +3311,15 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
+          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3341,15 +3341,15 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
+          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">

--- a/datasets/agenda_implementation/data/output/agenda_items.xlsx
+++ b/datasets/agenda_implementation/data/output/agenda_items.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Digital package</t>
+          <t>Revision of the Sustainable Finance Disclosure Regulation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>European Business Wallet</t>
+          <t>Digital package</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -755,22 +755,22 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Clean Industrial Deal</t>
+          <t>European Business Wallet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Simplification</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Action plan on affordable energy</t>
+          <t>Clean Industrial Deal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Industrial Decarbonisation Accelerator Act</t>
+          <t>Action plan on affordable energy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EU Start-up and Scale-up Strategy</t>
+          <t>Industrial Decarbonisation Accelerator Act</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Communication on a Savings and Investments Union</t>
+          <t>EU Start-up and Scale-up Strategy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Review of the Securitisation Framework</t>
+          <t>Communication on a Savings and Investments Union</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -983,17 +983,17 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Digital Networks Act</t>
+          <t>Review of the Securitisation Framework</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1021,7 +1021,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Continent Action Plan</t>
+          <t>Digital Networks Act</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Quantum Strategy of EU</t>
+          <t>AI Continent Action Plan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1097,12 +1097,12 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EU Space Act</t>
+          <t>Quantum Strategy of EU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bioeconomy Strategy</t>
+          <t>EU Space Act</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Non-legislative or legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Targeted revision of the REACH Regulation</t>
+          <t>Bioeconomy Strategy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Simplification</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative or legislative</t>
         </is>
       </c>
     </row>
@@ -1211,22 +1211,22 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roadmap towards ending Russian energy imports</t>
+          <t>Targeted revision of the REACH Regulation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Simplification</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -1249,17 +1249,17 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sustainable Transport Investment Plan</t>
+          <t>Roadmap towards ending Russian energy imports</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation A new era for European Defence and Security</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1287,17 +1287,17 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>White Paper on the Future of European Defence</t>
+          <t>Sustainable Transport Investment Plan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1325,12 +1325,12 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EU Preparedness Union Strategy</t>
+          <t>White Paper on the Future of European Defence</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Preparedness and Resilience</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1363,7 +1363,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Critical Medicines Act</t>
+          <t>EU Preparedness Union Strategy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Strategy to support medical countermeasures against public health threats</t>
+          <t>Critical Medicines Act</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EU Stockpiling Strategy</t>
+          <t>Strategy to support medical countermeasures against public health threats</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1477,17 +1477,17 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>New European Internal Security Strategy</t>
+          <t>EU Stockpiling Strategy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Preparedness and Resilience</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1515,7 +1515,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>New rules on drug precursors</t>
+          <t>New European Internal Security Strategy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Firearms Trafficking Directive</t>
+          <t>New rules on drug precursors</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1591,7 +1591,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Action plan on the cybersecurity of hospitals and healthcare providers</t>
+          <t>Firearms Trafficking Directive</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>New common approach on returns</t>
+          <t>Action plan on the cybersecurity of hospitals and healthcare providers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>European Migration and Asylum Strategy</t>
+          <t>New common approach on returns</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>A new action plan to implement the European Pillar of Social Rights</t>
+          <t>European Migration and Asylum Strategy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Social fairness</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1743,7 +1743,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Quality jobs roadmap</t>
+          <t>A new action plan to implement the European Pillar of Social Rights</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1781,17 +1781,17 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Union of Skills</t>
+          <t>Quality jobs roadmap</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Social fairness</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1819,17 +1819,17 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2030 Consumer Agenda, including an action plan for consumers in the Single Market</t>
+          <t>Union of Skills</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Social fairness Sustaining our quality of life: food security, water and nature</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1857,22 +1857,22 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>European Climate Law amendment</t>
+          <t>2030 Consumer Agenda, including an action plan for consumers in the Single Market</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Decarbonisation</t>
+          <t>Social fairness</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vision for Agriculture and Food</t>
+          <t>European Climate Law amendment</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Decarbonisation</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -1933,22 +1933,22 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Common Agricultural Policy simplification package</t>
+          <t>Vision for Agriculture and Food</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Simplification</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1971,12 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ocean Pact</t>
+          <t>Common Agricultural Policy simplification package</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Simplification</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>European Water Resilience Strategy</t>
+          <t>Ocean Pact</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preparedness and Resilience Protecting our democracy, upholding our values</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2047,17 +2047,17 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>European Democracy Shield</t>
+          <t>European Water Resilience Strategy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Preparedness and Resilience</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2085,7 +2085,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EU Strategy to support, protect and empower the civil society</t>
+          <t>European Democracy Shield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2123,17 +2123,17 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Roadmap for Women’s Rights</t>
+          <t>EU Strategy to support, protect and empower the civil society</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Equality</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2161,17 +2161,17 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>New equality strategies for LGBTIQ</t>
+          <t>Roadmap for Women’s Rights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Equality A global Europe: Leveraging our power and partnerships</t>
+          <t>Equality</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2199,17 +2199,17 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pact for the Mediterranean</t>
+          <t>New equality strategies for LGBTIQ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Equality</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2237,17 +2237,17 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EU strategic approach to the Black Sea/ Black Sea Strategy</t>
+          <t>Anti-racism</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Equality</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2275,17 +2275,17 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Joint Communication on a new Strategic EU-India Agenda</t>
+          <t>Pact for the Mediterranean</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Geopolitics Delivering together and preparing our Union for the future</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2313,22 +2313,22 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Post-2027 Multiannual Financial Framework proposals</t>
+          <t>EU strategic approach to the Black Sea/ Black Sea Strategy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Future priority</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cwp_annex_ii</t>
+          <t>cwp_annex_i</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2351,16 +2351,24 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fitness check on the legislative acquis in the digital policy area</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>Joint Communication on a new Strategic EU-India Agenda</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2370,7 +2378,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cwp_annex_ii</t>
+          <t>cwp_annex_i</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2381,16 +2389,24 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fitness check on energy security architecture</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>Post-2027 Multiannual Financial Framework proposals</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Future priority</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2400,7 +2416,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>cwp_annex_ii</t>
+          <t>cwp_annex_i</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2411,16 +2427,24 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fitness check on market access in inland waterway transport</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>An EU fit for enlargement: policy reviews and reforms</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Future priority</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Q2 / Q3 2025</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>tbd</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2441,7 +2465,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fitness Check of EU airports legislation</t>
+          <t>Fitness check on the legislative acquis in the digital policy area</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -2471,13 +2495,13 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Evaluation of the Public Procurement Directives</t>
+          <t>Fitness check on energy security architecture</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2501,13 +2525,13 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
+          <t>Fitness check on market access in inland waterway transport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 / Q3 2025</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2531,7 +2555,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
+          <t>Fitness Check of EU airports legislation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2561,13 +2585,13 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Evaluation of radioactive waste directives</t>
+          <t>Evaluation of the Public Procurement Directives</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -2591,7 +2615,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
+          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -2621,13 +2645,13 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Evaluation of the EU Lifts Directive</t>
+          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2651,13 +2675,13 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
+          <t>Evaluation of radioactive waste directives</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2681,7 +2705,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
+          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2711,13 +2735,13 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Evaluation of the Fishing Vessel Safety Directive</t>
+          <t>Evaluation of the EU Lifts Directive</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Q1/Q2 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -2741,13 +2765,13 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
+          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2771,7 +2795,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Evaluation of State aid rules for banks in difficulties</t>
+          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -2801,13 +2825,13 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Evaluation of the Guarantee Notice</t>
+          <t>Evaluation of the Fishing Vessel Safety Directive</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q1/Q2 2025</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -2831,7 +2855,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
+          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2861,7 +2885,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Evaluation of EU Rules of Origin</t>
+          <t>Evaluation of State aid rules for banks in difficulties</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2891,13 +2915,13 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Evaluation of the Defence Transfers Directive</t>
+          <t>Evaluation of the Guarantee Notice</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -2921,7 +2945,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Evaluation of the Firearms Directive</t>
+          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2951,7 +2975,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Evaluation on the Innovation Fund</t>
+          <t>Evaluation of EU Rules of Origin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2981,7 +3005,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Evaluation on the Modernisation Fund</t>
+          <t>Evaluation of the Defence Transfers Directive</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -3011,13 +3035,13 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
+          <t>Evaluation of the Firearms Directive</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3041,13 +3065,13 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
+          <t>Evaluation on the Innovation Fund</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Q3/Q4 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3071,13 +3095,13 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
+          <t>Evaluation on the Modernisation Fund</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3101,13 +3125,13 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
+          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3131,13 +3155,13 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
+          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3/Q4 2025</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -3161,7 +3185,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
+          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3191,7 +3215,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
+          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -3221,13 +3245,13 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
+          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3251,13 +3275,13 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Interim Evaluation of the European Defence Fund</t>
+          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Q1-Q2 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -3281,13 +3305,13 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Customs 2021-2027 programme</t>
+          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3311,13 +3335,13 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
+          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3341,13 +3365,13 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
+          <t>Interim Evaluation of the European Defence Fund</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1-Q2 2025</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3360,7 +3384,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cwp_annex_iii</t>
+          <t>cwp_annex_ii</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3371,13 +3395,13 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Horizon Europe framework programme for Research and Innovation</t>
+          <t>Interim evaluation of the Customs 2021-2027 programme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -3390,7 +3414,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>cwp_annex_iii</t>
+          <t>cwp_annex_ii</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3401,7 +3425,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mid-term evaluation of the European Regional Development Fund, the Cohesion Fund and the Just Transition Fund 2021-2027</t>
+          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -3420,7 +3444,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>cwp_annex_iii</t>
+          <t>cwp_annex_ii</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3431,13 +3455,13 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mid-term evaluation of the European Social Fund Plus 2021-2027</t>
+          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -3450,7 +3474,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>cwp_annex_iv</t>
+          <t>cwp_annex_ii</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3461,20 +3485,16 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>COM(2011)714 final Proposal for a COUNCIL DIRECTIVE on a common system of taxation Obsolete – the scope of the proposal has been partly</t>
+          <t>Interim evaluation of the Horizon Europe framework programme for Research and Innovation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3484,7 +3504,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>cwp_annex_iv</t>
+          <t>cwp_annex_ii</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3495,20 +3515,16 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>COM(2011)827 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the proposal is by now obsolete. The</t>
+          <t>Mid-term evaluation of the European Regional Development Fund, the Cohesion Fund and the Just Transition Fund 2021-2027</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3518,7 +3534,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>cwp_annex_iv</t>
+          <t>cwp_annex_ii</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3529,20 +3545,16 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>COM(2012)336 final Proposal for a COUNCIL REGULATION establishing a facility for providing Obsolete – the proposal needs to be updated as regards</t>
+          <t>Mid-term evaluation of the European Social Fund Plus 2021-2027</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3563,18 +3575,14 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>COM(2015)603 final Proposal for a COUNCIL DECISION laying down measures in view of No foreseeable agreement – in the context of the</t>
+          <t>Proposal for a COUNCIL DIRECTIVE on a common system of taxation applicable to interest and royalty payments made between associated companies of different Member States</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
     </row>
@@ -3597,18 +3605,14 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>COM(2017)276 final Proposal for a COUNCIL DIRECTIVE amending Directive 1999/62/EC on the No foreseeable agreement – the proposal is blocked with</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on common rules for the allocation of slots at European Union airports</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -3631,15 +3635,11 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>COM(2017)647 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal has not been</t>
+          <t>Proposal for a COUNCIL REGULATION establishing a facility for providing financial assistance for Member States whose currency is not the euro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -3665,18 +3665,14 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>COM(2017)827 final Proposal for a COUNCIL REGULATION on the establishment of the European No foreseeable agreement - many of the changes</t>
+          <t>Proposal for a COUNCIL DECISION laying down measures in view of progressively establishing unified representation of the euro area in the International Monetary Fund</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
@@ -3699,15 +3695,11 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>COM(2018)135 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a COUNCIL DIRECTIVE amending Directive 1999/62/EC on the charging of heavy goods vehicles for the use of certain infrastructures, as regards certain provisions on vehicle taxation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>DIRECTIVE</t>
@@ -3733,18 +3725,14 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>COM(2018)329 final Proposal for a COUNCIL DIRECTIVE amending Directive 2006/112/EC as No foreseeable agreement – discussions are suspended</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EC) No 1073/2009 on common rules for access to the international market for coach and bus services</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -3767,15 +3755,11 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>COM(2018)339 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a COUNCIL REGULATION on the establishment of the European Monetary Fund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -3801,18 +3785,14 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>COM(2018)387 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - The proposal is outdated</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on credit servicers, credit purchasers and the recovery of collateral</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
     </row>
@@ -3835,18 +3815,14 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>COM(2019)38 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
+          <t>Proposal for a COUNCIL DIRECTIVE amending Directive 2006/112/EC as regards the introduction of the detailed technical measures for the operation of the definitive VAT system for the taxation of trade between Member States</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
     </row>
@@ -3869,18 +3845,14 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>COM(2020)49 final Proposal for a COUNCIL DIRECTIVE on administrative cooperation in the field Obsolete - since the adoption of this proposal in 2020, a</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on sovereign bond-backed securities</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -3903,15 +3875,11 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>COM(2020)577 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on the establishment of a European Investment Stabilisation Function</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -3937,18 +3905,14 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>COM(2021)769 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - since the adoption of this proposal in 2021, a</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) 2015/757 in order to take appropriate account of the global data collection system for ship fuel oil consumption data</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -3971,15 +3935,11 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>COM(2022)222 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the changes suggested by this proposal were</t>
+          <t>Proposal for a COUNCIL DIRECTIVE on administrative cooperation in the field of taxation (codification)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>DIRECTIVE</t>
@@ -4005,15 +3965,11 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>COM(2023)232 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) 2018/1139 as regards the capacity of the European Union Aviation Safety Agency to act as Performance Review Body of the Single European Sky</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4039,15 +3995,11 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>COM(2018)634 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the Commission intends to present a new</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL laying down for certain road vehicles circulating within the Union the maximum authorised dimensions in national and international traffic and the maximum authorised weights in international traffic (codification)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>DIRECTIVE</t>
@@ -4073,18 +4025,14 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>COM(2021)890 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the content of this proposal was merged into</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Directive (EU) 2018/2001 on the promotion of the use of energy from renewable sources, Directive 2010/31/EU on the energy performance of buildings and Directive 2012/27/EU on energy efficiency</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
     </row>
@@ -4107,18 +4055,14 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>COM(2021)752 final Proposal for a COUNCIL DECISION on provisional emergency measures for Obsolete – the proposal was blocked during the inter-</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on standard essential patents and amending Regulation (EU)2017/1001</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -4141,18 +4085,14 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>COM(2024)174 final Proposal for a COUNCIL RECOMMENDATION for the 2024/2025 Schengen Obsolete – no agreement was foreseeable. The Schengen</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on common standards and procedures in Member States for returning illegally staying third-country nationals (recast) A contribution from the European Commission to the Leaders’ meeting in Salzburg on 19-20 September 2018</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>RECOMMENDATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
     </row>
@@ -4175,15 +4115,11 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>COM(2012)403 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL addressing situations of instrumentalisation in the field of migration and asylum</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4209,18 +4145,14 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>COM(2015)177 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - any potential further</t>
+          <t>Proposal for a COUNCIL DECISION on provisional emergency measures for the benefit of Latvia, Lithuania and Poland</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
@@ -4243,18 +4175,14 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>COM(2022)563 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>Proposal for a COUNCIL RECOMMENDATION for the 2024/2025 Schengen Cycle</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>RECOMMENDATION</t>
         </is>
       </c>
     </row>
@@ -4277,15 +4205,11 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>COM(2023)771 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on the protection of species of wild fauna and flora by regulating trade therein (Recast)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4311,18 +4235,14 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>COM(2008)426 final Proposal for a COUNCIL DIRECTIVE on implementing the principle of equal No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EC) No 1829/2003 as regards the possibility for the Member States to restrict or prohibit the use of genetically modified food and feed on their territory</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -4345,15 +4265,11 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>COM(2011)137 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement - no progress has been made</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL laying down management, conservation and control measures applicable in the Area of the Southern Indian Ocean Fisheries Agreement (SIOFA)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4379,15 +4295,11 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>COM(2016)799 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulations (EU) 2016/1139, (EU) 2018/973 and (EU) 2019/472 as regards the targets for fixing fishing opportunities</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4413,18 +4325,14 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>COM(2017)10 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>Proposal for a COUNCIL DIRECTIVE on implementing the principle of equal treatment between persons irrespective of religion or belief, disability, age or sexual orientation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
     </row>
@@ -4447,15 +4355,11 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>COM(2017)85 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EC) No 1049/2001 regarding public access to European Parliament, Council and Commission documents</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4481,15 +4385,11 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>COM(2018)96 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL adapting a number of legal acts providing for the use of the regulatory procedure with scrutiny to Articles 290 and 291 of the Treaty on the Functioning of the European Union</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4515,18 +4415,14 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>COM(2022)496 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL concerning the respect for private life and the protection of personal data in electronic communications and repealing Directive 2002/58/EC (Regulation on Privacy and Electronic Communications</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -4549,18 +4445,14 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>JOIN(2015)36 final Joint Proposal for a COUNCIL DECISION on the conclusion, on behalf of the Obsolete – the ratification process of this agreement has</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) No 182/2011 laying down the rules and general principles concerning mechanisms for control by Member States of the Commission’s exercise of implementing powers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -4583,18 +4475,14 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>COM(2022)63 final Proposal for a COUNCIL DECISION on the position to be taken on behalf of the Obsolete - the proposal was made in the negotiations on</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on the law applicable to the third-party effects of assignments of claims</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -4617,18 +4505,14 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>COM(2022)184 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the content of the proposal has been adopted</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on adapting non-contractual civil liability rules to artificial intelligence (AI Liability)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
     </row>
@@ -4651,18 +4535,14 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>COM(2024)301 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>Joint Proposal for a COUNCIL DECISION on the conclusion, on behalf of the European Union, of the Cooperation Agreement on Partnership and Development between the European Union and the Islamic Republic of Afghanistan</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
@@ -4685,18 +4565,14 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>COM(2024)100 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>Proposal for a COUNCIL DECISION on the position to be taken on behalf of the European Union in the written procedure by the Participants to the Arrangement on Officially Supported Export Credits amending Annex IV</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
@@ -4719,15 +4595,11 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Agriculture Council Regulation (EC)No 870/2004 of 26 This Community programme was established for the period 2004 to 2006 to complement and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU, Euratom) 2018/1046 on the financial rules applicable to the general budget of the Union</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4753,15 +4625,11 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>European statistics Council Regulation (EEC) No 3037/90 of 9 The classification from 1990 is obsolete. The current statistical classification of economic</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) 2021/1148 as regards the financial envelope and the allocation for the thematic facility</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4787,14 +4655,14 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>European statistics Council Decision of 25 June 1996 on improving The Decision is obsolete. It has been superseded by new regulations on agricultural statistics</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) No 2021/522, Regulation (EU) No 2021/1057, Regulation (EU) No 2021/1060, Regulation (EU) No 2021/1139, Regulation (EU) No 2021/1229 and Regulation (EU) No 2021/1775 as regards the changes to the amounts of funds for certain programmes and funds</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>REGULATION</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4674,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>cwp_annex_iv</t>
+          <t>cwp_annex_v</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4817,15 +4685,15 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Road freight Council Regulation (EEC) No 4058/89 of 21 Modern EU legislation has introduced a comprehensive framework that regulates road transport,</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
+          <t>Council Regulation (EC)No 870/2004 of 26 April 2004 establishing a Community programme on the conservation, characterisation, collection and utilisation of genetic resources in agriculture and repealing Regulation (EC) No 1467/94</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>REGULATION</t>
@@ -4840,27 +4708,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>mission_letter</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>C0003</t>
-        </is>
-      </c>
+          <t>cwp_annex_v</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>WP128</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>take forward the Commission’s work to improve access to secure, fast, and reliable connectivity, as...</t>
+          <t>Council Regulation (EEC) No 3037/90 of 9 October 1990 on the statistical classification of economic activities in the European Community</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Tech Sovereignty, Security and Democracy</t>
+          <t>European statistics</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4870,27 +4742,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>mission_letter</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>C0017</t>
-        </is>
-      </c>
+          <t>cwp_annex_v</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>WP129</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>As part of boosting high performance computing and quantum, you will develop the proposal in the...</t>
+          <t>Council Decision of 25 June 1996 on improving Community agricultural statistics (96/411/EC)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Tech Sovereignty, Security and Democracy</t>
+          <t>European statistics</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4900,27 +4776,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>mission_letter</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>C0027</t>
-        </is>
-      </c>
+          <t>cwp_annex_v</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>WP130</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>Council Regulation (EEC) No 4058/89 of 21 December 1989 on the fixing of rates for the carriage of goods by road between Member States</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Tech Sovereignty, Security and Democracy</t>
+          <t>Road freight transport</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4936,17 +4816,17 @@
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>C0050</t>
+          <t>C0003</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>propose to revise State aid rules to enable housing support measures, notably for energy efficiency...</t>
+          <t>take forward the Commission’s work to improve access to secure, fast, and reliable connectivity,...</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Clean, Just and Competitive Transition</t>
+          <t>Executive Vice-President for Tech Sovereignty, Security and Democracy</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -4966,17 +4846,17 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>C0067</t>
+          <t>C0017</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>As part of boosting high performance computing and quantum, you will develop the proposal in the...</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Clean, Just and Competitive Transition</t>
+          <t>Executive Vice-President for Tech Sovereignty, Security and Democracy</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -4996,17 +4876,17 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>C0091</t>
+          <t>C0027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>As part of this, you will present an Industrial Decarbonisation Accelerator Act, to support...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Prosperity and Industrial Strategy</t>
+          <t>Executive Vice-President for Tech Sovereignty, Security and Democracy</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -5026,17 +4906,17 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>C0093</t>
+          <t>C0050</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>revise the Public Procurement Directives to help ensure security of supply for certain vital...</t>
+          <t>propose to revise State aid rules to enable housing support measures, notably for energy...</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Prosperity and Industrial Strategy</t>
+          <t>Executive Vice-President for Clean, Just and Competitive Transition</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -5056,7 +4936,7 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>C0114</t>
+          <t>C0067</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5066,7 +4946,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Prosperity and Industrial Strategy</t>
+          <t>Executive Vice-President for Clean, Just and Competitive Transition</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -5086,17 +4966,17 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>C0141</t>
+          <t>C0091</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>More broadly, I want you to work with the Commission to ensure that we can react flexibly to new...</t>
+          <t>As part of this, you will present an Industrial Decarbonisation Accelerator Act, to support...</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>High Representative / Vice-President for Foreign Affairs and Security Policy</t>
+          <t>Executive Vice-President for Prosperity and Industrial Strategy</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -5116,17 +4996,17 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>C0156</t>
+          <t>C0093</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>revise the Public Procurement Directives to help ensure security of supply for certain vital...</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>High Representative / Vice-President for Foreign Affairs and Security Policy</t>
+          <t>Executive Vice-President for Prosperity and Industrial Strategy</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -5146,7 +5026,7 @@
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>C0192</t>
+          <t>C0114</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5156,7 +5036,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Executive Vice-President for Cohesion and Reforms</t>
+          <t>Executive Vice-President for Prosperity and Industrial Strategy</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -5176,17 +5056,17 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>C0225</t>
+          <t>C0141</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>I would also like you to focus on the impact of digitalisation in the world of work. This should...</t>
+          <t>More broadly, I want you to work with the Commission to ensure that we can react flexibly to new...</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Executive Vice-President for People, Skills and Preparedness</t>
+          <t>High Representative / Vice-President for Foreign Affairs and Security Policy</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -5206,7 +5086,7 @@
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>C0239</t>
+          <t>C0156</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5216,7 +5096,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Executive Vice-President for People, Skills and Preparedness</t>
+          <t>High Representative / Vice-President for Foreign Affairs and Security Policy</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -5236,17 +5116,17 @@
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>C0273</t>
+          <t>C0192</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>lead the Commission’s work to revise the Framework Agreement on relations between the Parliament...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Commissioner for Trade and Economic Security, Interinstitutional Relations and Transparency</t>
+          <t>Executive Vice-President for Cohesion and Reforms</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -5266,17 +5146,17 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>C0293</t>
+          <t>C0225</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>I would also like you to focus on the impact of digitalisation in the world of work. This should...</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Commissioner for Trade and Economic Security, Interinstitutional Relations and Transparency</t>
+          <t>Executive Vice-President for People, Skills and Preparedness</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -5296,7 +5176,7 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>C0343</t>
+          <t>C0239</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5306,7 +5186,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Commissioner for Economy and Productivity, and Implementation</t>
+          <t>Executive Vice-President for People, Skills and Preparedness</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -5326,17 +5206,17 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>C0376</t>
+          <t>C0273</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>lead the Commission’s work to revise the Framework Agreement on relations between the Parliament...</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Commissioner for Mediterranean</t>
+          <t>Commissioner for Trade and Economic Security, Interinstitutional Relations and Transparency</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -5356,7 +5236,7 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>C0426</t>
+          <t>C0293</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5366,7 +5246,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Commissioner for Preparedness and Crisis Management, Equality</t>
+          <t>Commissioner for Trade and Economic Security, Interinstitutional Relations and Transparency</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -5386,17 +5266,17 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>C0446</t>
+          <t>C0343</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>propose to enshrine the 90% emission-reduction target for 2040 in our European Climate Law....</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Commissioner for Climate, Net Zero and Clean Growth</t>
+          <t>Commissioner for Economy and Productivity, and Implementation</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -5416,17 +5296,17 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>C0450</t>
+          <t>C0376</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>lead the work to level the energy taxation playing field and the strategic use of taxation measures...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Commissioner for Climate, Net Zero and Clean Growth</t>
+          <t>Commissioner for Mediterranean</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -5446,17 +5326,17 @@
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>C0451</t>
+          <t>C0426</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>The 2035 climate neutrality for cars creates predictability for investors and manufacturers. You...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Commissioner for Climate, Net Zero and Clean Growth</t>
+          <t>Commissioner for Preparedness and Crisis Management, Equality</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -5476,12 +5356,12 @@
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>C0461</t>
+          <t>C0446</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>continue the work on the reform of corporate taxation, including by concluding the negotiations on...</t>
+          <t>propose to enshrine the 90% emission-reduction target for 2040 in our European Climate Law....</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5506,12 +5386,12 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>C0465</t>
+          <t>C0450</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>lead the work to level the energy taxation playing field and the strategic use of taxation...</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5536,17 +5416,17 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>C0501</t>
+          <t>C0451</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>The 2035 climate neutrality for cars creates predictability for investors and manufacturers. You...</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Commissioner for International Partnerships</t>
+          <t>Commissioner for Climate, Net Zero and Clean Growth</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -5566,17 +5446,17 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>C0524</t>
+          <t>C0461</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Building upon the existing animal welfare legislation, you will modernise the rules on animal...</t>
+          <t>continue the work on the reform of corporate taxation, including by concluding the negotiations...</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Commissioner for Health and Animal Welfare</t>
+          <t>Commissioner for Climate, Net Zero and Clean Growth</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -5596,17 +5476,17 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>C0528</t>
+          <t>C0465</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>propose a Critical Medicines Act to address the severe shortages of medicines and medical devices...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Commissioner for Health and Animal Welfare</t>
+          <t>Commissioner for Climate, Net Zero and Clean Growth</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -5626,17 +5506,17 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>C0530</t>
+          <t>C0501</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>lead the work on a new European Biotech Act, focusing on the need for a regulatory environment...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Commissioner for Health and Animal Welfare</t>
+          <t>Commissioner for International Partnerships</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -5656,12 +5536,12 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>C0538</t>
+          <t>C0524</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>Building upon the existing animal welfare legislation, you will modernise the rules on animal...</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5686,17 +5566,17 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>C0571</t>
+          <t>C0528</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>propose a Critical Medicines Act to address the severe shortages of medicines and medical...</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Commissioner for Enlargement</t>
+          <t>Commissioner for Health and Animal Welfare</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -5716,17 +5596,17 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>C0598</t>
+          <t>C0530</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>To support this, you will support the Executive Vice-President for Cohesion and Reforms on a...</t>
+          <t>lead the work on a new European Biotech Act, focusing on the need for a regulatory environment...</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Commissioner for Energy and Housing</t>
+          <t>Commissioner for Health and Animal Welfare</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -5746,17 +5626,17 @@
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>C0602</t>
+          <t>C0538</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>make proposals to incentivise and increase the uptake of carbon capture utilisation and storage...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Commissioner for Energy and Housing</t>
+          <t>Commissioner for Health and Animal Welfare</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -5776,17 +5656,17 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>C0604</t>
+          <t>C0571</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>propose an initiative to boost the roll out of renewable energy and energy storage. You will work...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Commissioner for Energy and Housing</t>
+          <t>Commissioner for Enlargement</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -5806,12 +5686,12 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>C0610</t>
+          <t>C0598</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>tackle systemic issues with short-term accommodation rentals and make proposals to tackle the...</t>
+          <t>To support this, you will support the Executive Vice-President for Cohesion and Reforms on a...</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5836,12 +5716,12 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>C0616</t>
+          <t>C0602</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>make proposals to incentivise and increase the uptake of carbon capture utilisation and storage...</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5866,17 +5746,17 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>C0652</t>
+          <t>C0604</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>propose an initiative to boost the roll out of renewable energy and energy storage. You will...</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Commissioner for Fisheries and Oceans</t>
+          <t>Commissioner for Energy and Housing</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -5896,17 +5776,17 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>C0671</t>
+          <t>C0610</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>lead work on taking forward our zero-pollution ambition. As part of this, you will work with the...</t>
+          <t>tackle systemic issues with short-term accommodation rentals and make proposals to tackle the...</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Commissioner for Environment, Water Resilience and a Competitive Circular Economy</t>
+          <t>Commissioner for Energy and Housing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -5926,17 +5806,17 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>C0672</t>
+          <t>C0616</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>As part of your work in contributing to the Clean Industrial Deal, you will lead, with the...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Commissioner for Environment, Water Resilience and a Competitive Circular Economy</t>
+          <t>Commissioner for Energy and Housing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -5956,7 +5836,7 @@
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>C0685</t>
+          <t>C0652</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5966,7 +5846,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Commissioner for Environment, Water Resilience and a Competitive Circular Economy</t>
+          <t>Commissioner for Fisheries and Oceans</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
@@ -5986,17 +5866,17 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>C0726</t>
+          <t>C0671</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>lead work on taking forward our zero-pollution ambition. As part of this, you will work with the...</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Commissioner for Budget, Anti-Fraud, and Public Administration</t>
+          <t>Commissioner for Environment, Water Resilience and a Competitive Circular Economy</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
@@ -6016,17 +5896,17 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>C0754</t>
+          <t>C0672</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>prepare a proposal for a Single Digital Booking and Ticketing Regulation to ensure that Europeans...</t>
+          <t>As part of your work in contributing to the Clean Industrial Deal, you will lead, with the...</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Commissioner for Sustainable Transport and Tourism</t>
+          <t>Commissioner for Environment, Water Resilience and a Competitive Circular Economy</t>
         </is>
       </c>
       <c r="G168" t="inlineStr"/>
@@ -6046,7 +5926,7 @@
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>C0766</t>
+          <t>C0685</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6056,7 +5936,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Commissioner for Sustainable Transport and Tourism</t>
+          <t>Commissioner for Environment, Water Resilience and a Competitive Circular Economy</t>
         </is>
       </c>
       <c r="G169" t="inlineStr"/>
@@ -6076,17 +5956,17 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>C0783</t>
+          <t>C0726</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>put forward proposals for clean corporate fleets.</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Commissioner for Sustainable Transport and Tourism</t>
+          <t>Commissioner for Budget, Anti-Fraud, and Public Administration</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
@@ -6106,17 +5986,17 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>C0788</t>
+          <t>C0754</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>focus on the impact and opportunities of digital technologies on consumers and our justice system....</t>
+          <t>prepare a proposal for a Single Digital Booking and Ticketing Regulation to ensure that...</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Commissioner for Democracy, Justice, the Rule of Law, and Consumer Protection</t>
+          <t>Commissioner for Sustainable Transport and Tourism</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
@@ -6136,17 +6016,17 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>C0794</t>
+          <t>C0766</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>also focus on the implementation of the European Media Freedom Act and put forward proposals to...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Commissioner for Democracy, Justice, the Rule of Law, and Consumer Protection</t>
+          <t>Commissioner for Sustainable Transport and Tourism</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
@@ -6166,17 +6046,17 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>C0800</t>
+          <t>C0783</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>lead the work to build an EU-wide legal status to help innovative companies grow, taking the form...</t>
+          <t>put forward proposals for clean corporate fleets.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Commissioner for Democracy, Justice, the Rule of Law, and Consumer Protection</t>
+          <t>Commissioner for Sustainable Transport and Tourism</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -6196,12 +6076,12 @@
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>C0805</t>
+          <t>C0788</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>strengthen the European Arrest Warrant to allow judicial authorities to work more closely and to...</t>
+          <t>focus on the impact and opportunities of digital technologies on consumers and our justice...</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6226,12 +6106,12 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>C0812</t>
+          <t>C0794</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>also focus on the implementation of the European Media Freedom Act and put forward proposals to...</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6256,17 +6136,17 @@
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>C0832</t>
+          <t>C0800</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>As part of this, you will ensure law enforcement and judicial cooperation is strengthened. You will...</t>
+          <t>lead the work to build an EU-wide legal status to help innovative companies grow, taking the...</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Commissioner for Internal Affairs and Migration</t>
+          <t>Commissioner for Democracy, Justice, the Rule of Law, and Consumer Protection</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -6286,17 +6166,17 @@
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>C0837</t>
+          <t>C0805</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>develop a new common approach on the return of irregular migrants, with new modern rules to speed...</t>
+          <t>strengthen the European Arrest Warrant to allow judicial authorities to work more closely and to...</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Commissioner for Internal Affairs and Migration</t>
+          <t>Commissioner for Democracy, Justice, the Rule of Law, and Consumer Protection</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
@@ -6316,17 +6196,17 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>C0853</t>
+          <t>C0812</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>update law enforcement’s tools for access to digital information and rules on data retention, while...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Commissioner for Internal Affairs and Migration</t>
+          <t>Commissioner for Democracy, Justice, the Rule of Law, and Consumer Protection</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -6346,12 +6226,12 @@
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>C0861</t>
+          <t>C0832</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>As part of this, you will ensure law enforcement and judicial cooperation is strengthened. You...</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6376,17 +6256,17 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>C0887</t>
+          <t>C0837</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>propose to update the Council Recommendation on Health Enhancing Physical Activity, notably to...</t>
+          <t>develop a new common approach on the return of irregular migrants, with new modern rules to...</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Commissioner for Intergenerational Fairness, Youth, Culture and Sport</t>
+          <t>Commissioner for Internal Affairs and Migration</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
@@ -6406,17 +6286,17 @@
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>C0888</t>
+          <t>C0853</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>make proposals to make it easier for people, in particular the younger generation, to visit and the...</t>
+          <t>update law enforcement’s tools for access to digital information and rules on data retention,...</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Commissioner for Intergenerational Fairness, Youth, Culture and Sport</t>
+          <t>Commissioner for Internal Affairs and Migration</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -6436,7 +6316,7 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>C0894</t>
+          <t>C0861</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6446,7 +6326,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Commissioner for Intergenerational Fairness, Youth, Culture and Sport</t>
+          <t>Commissioner for Internal Affairs and Migration</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -6466,17 +6346,17 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>C0929</t>
+          <t>C0887</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>propose to update the Council Recommendation on Health Enhancing Physical Activity, notably to...</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Commissioner for Agriculture and Food</t>
+          <t>Commissioner for Intergenerational Fairness, Youth, Culture and Sport</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
@@ -6496,17 +6376,17 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>C0951</t>
+          <t>C0888</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Applying and deploying innovation matters for competitiveness. You will work on a European...</t>
+          <t>make proposals to make it easier for people, in particular the younger generation, to visit and...</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Commissioner for Startups, Research and Innovation</t>
+          <t>Commissioner for Intergenerational Fairness, Youth, Culture and Sport</t>
         </is>
       </c>
       <c r="G184" t="inlineStr"/>
@@ -6526,17 +6406,17 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>C0954</t>
+          <t>C0894</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>propose a European Research Area Act to guarantee a “fifth freedom”, namely the free movement of...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Commissioner for Startups, Research and Innovation</t>
+          <t>Commissioner for Intergenerational Fairness, Youth, Culture and Sport</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
@@ -6556,17 +6436,17 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>C0955</t>
+          <t>C0929</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Reflecting the growing importance and demand for advanced materials to support the competitiveness...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Commissioner for Startups, Research and Innovation</t>
+          <t>Commissioner for Agriculture and Food</t>
         </is>
       </c>
       <c r="G186" t="inlineStr"/>
@@ -6586,12 +6466,12 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>C0965</t>
+          <t>C0951</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>Applying and deploying innovation matters for competitiveness. You will work on a European...</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6616,17 +6496,17 @@
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>C1001</t>
+          <t>C0954</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+          <t>propose a European Research Area Act to guarantee a “fifth freedom”, namely the free movement of...</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Commissioner for Financial Services and the Savings and Investments Union</t>
+          <t>Commissioner for Startups, Research and Innovation</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -6646,17 +6526,17 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>C1021</t>
+          <t>C0955</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>work on creating a true Single Market for Defence products and services, enhancing production...</t>
+          <t>Reflecting the growing importance and demand for advanced materials to support the...</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Commissioner for Defence and Space</t>
+          <t>Commissioner for Startups, Research and Innovation</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
@@ -6676,17 +6556,17 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>C1028</t>
+          <t>C0965</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>lead the work on a future proposal for an EU Space Law. In this context, as proposed in the Draghi...</t>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Commissioner for Defence and Space</t>
+          <t>Commissioner for Startups, Research and Innovation</t>
         </is>
       </c>
       <c r="G190" t="inlineStr"/>
@@ -6706,7 +6586,7 @@
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>C1039</t>
+          <t>C1001</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6716,11 +6596,101 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Commissioner for Defence and Space</t>
+          <t>Commissioner for Financial Services and the Savings and Investments Union</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>AI0191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>mission_letter</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>C1021</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>work on creating a true Single Market for Defence products and services, enhancing production...</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Commissioner for Defence and Space</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>AI0192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>mission_letter</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>C1028</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>lead the work on a future proposal for an EU Space Law. In this context, as proposed in the...</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Commissioner for Defence and Space</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>AI0193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>mission_letter</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>C1039</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>also work to stress test the EU acquis and table proposals to eliminate any overlaps and...</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Commissioner for Defence and Space</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
